--- a/src/main/resources/templates/job_import_template.xlsx
+++ b/src/main/resources/templates/job_import_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>职位名称*</t>
   </si>
@@ -62,10 +62,7 @@
     <t>联系邮箱</t>
   </si>
   <si>
-    <t>岗位职责</t>
-  </si>
-  <si>
-    <t>任职要求</t>
+    <t>职位信息</t>
   </si>
   <si>
     <t>福利待遇</t>
@@ -93,9 +90,6 @@
   </si>
   <si>
     <t>负责公司产品后端开发</t>
-  </si>
-  <si>
-    <t>熟练掌握Java和Spring Boot</t>
   </si>
   <si>
     <t>五险一金、弹性工作</t>
@@ -1270,7 +1264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="22.175" customWidth="1"/>
@@ -1281,11 +1275,10 @@
     <col min="10" max="10" width="16.0083333333333" customWidth="1"/>
     <col min="11" max="11" width="26.8416666666667" customWidth="1"/>
     <col min="12" max="12" width="23.675" customWidth="1"/>
-    <col min="13" max="13" width="26.175" customWidth="1"/>
-    <col min="14" max="14" width="22.0083333333333" customWidth="1"/>
+    <col min="13" max="13" width="22.0083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:14">
+    <row r="1" ht="22.5" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1325,16 +1318,13 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C2" s="2">
         <v>15000</v>
@@ -1343,34 +1333,31 @@
         <v>25000</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2">
         <v>13800138000</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/templates/job_import_template.xlsx
+++ b/src/main/resources/templates/job_import_template.xlsx
@@ -27,54 +27,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>职位名称*</t>
-  </si>
-  <si>
-    <t>公司名称*</t>
-  </si>
-  <si>
-    <t>薪资下限*</t>
-  </si>
-  <si>
-    <t>薪资上限*</t>
-  </si>
-  <si>
-    <t>工作地点*</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>单位名称*</t>
+  </si>
+  <si>
+    <t>工种名称*</t>
+  </si>
+  <si>
+    <t>工种类别</t>
+  </si>
+  <si>
+    <t>招聘人数</t>
+  </si>
+  <si>
+    <t>月薪下限*</t>
+  </si>
+  <si>
+    <t>月薪上限*</t>
+  </si>
+  <si>
+    <t>福利待遇</t>
+  </si>
+  <si>
+    <t>职位简介</t>
+  </si>
+  <si>
+    <t>工作性质</t>
   </si>
   <si>
     <t>学历要求</t>
   </si>
   <si>
-    <t>工作经验</t>
-  </si>
-  <si>
-    <t>招聘人数</t>
+    <t>经验要求</t>
   </si>
   <si>
     <t>联系人</t>
   </si>
   <si>
-    <t>联系电话*</t>
-  </si>
-  <si>
-    <t>联系邮箱</t>
-  </si>
-  <si>
-    <t>职位信息</t>
-  </si>
-  <si>
-    <t>福利待遇</t>
+    <t>联系手机*</t>
+  </si>
+  <si>
+    <t>电子邮箱</t>
+  </si>
+  <si>
+    <t>某科技有限公司</t>
   </si>
   <si>
     <t>Java后端开发工程师</t>
   </si>
   <si>
-    <t>某科技有限公司</t>
-  </si>
-  <si>
-    <t>北京</t>
+    <t>五险一金、弹性工作</t>
+  </si>
+  <si>
+    <t>负责公司产品后端开发</t>
+  </si>
+  <si>
+    <t>不限</t>
   </si>
   <si>
     <t>本科</t>
@@ -87,12 +96,6 @@
   </si>
   <si>
     <t>zhangsan@example.com</t>
-  </si>
-  <si>
-    <t>负责公司产品后端开发</t>
-  </si>
-  <si>
-    <t>五险一金、弹性工作</t>
   </si>
 </sst>
 </file>
@@ -1264,21 +1267,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="22.175" customWidth="1"/>
     <col min="2" max="2" width="16.675" customWidth="1"/>
-    <col min="3" max="5" width="13.175" customWidth="1"/>
-    <col min="6" max="8" width="12.3416666666667" customWidth="1"/>
+    <col min="3" max="3" width="17.75" customWidth="1"/>
+    <col min="4" max="5" width="13.175" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="21.25" customWidth="1"/>
+    <col min="8" max="8" width="24.875" customWidth="1"/>
     <col min="9" max="9" width="13.175" customWidth="1"/>
     <col min="10" max="10" width="16.0083333333333" customWidth="1"/>
     <col min="11" max="11" width="26.8416666666667" customWidth="1"/>
     <col min="12" max="12" width="23.675" customWidth="1"/>
     <col min="13" max="13" width="22.0083333333333" customWidth="1"/>
+    <col min="14" max="14" width="28.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:13">
+    <row r="1" ht="15" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1318,46 +1325,52 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:13">
+    <row r="2" ht="16.5" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="2">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
         <v>15000</v>
       </c>
-      <c r="D2" s="2">
+      <c r="F2" s="2">
         <v>25000</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="2">
-        <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="2">
         <v>13800138000</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>21</v>
+      <c r="N2" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/templates/job_import_template.xlsx
+++ b/src/main/resources/templates/job_import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17490"/>
+    <workbookView windowWidth="31335" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="job_import_template" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>展位号码</t>
+  </si>
   <si>
     <t>单位名称*</t>
+  </si>
+  <si>
+    <t>职位行政区划</t>
   </si>
   <si>
     <t>工种名称*</t>
@@ -74,6 +80,9 @@
     <t>某科技有限公司</t>
   </si>
   <si>
+    <t>吉林省松原市</t>
+  </si>
+  <si>
     <t>Java后端开发工程师</t>
   </si>
   <si>
@@ -102,7 +111,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="7" formatCode="&quot;￥&quot;#,##0.00;&quot;￥&quot;\-#,##0.00"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -468,12 +478,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -600,7 +625,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -612,34 +637,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -724,15 +749,36 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="7" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1267,111 +1313,2105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:P113"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.175" customWidth="1"/>
+    <col min="1" max="1" width="12.3416666666667" customWidth="1"/>
     <col min="2" max="2" width="16.675" customWidth="1"/>
-    <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="5" width="13.175" customWidth="1"/>
-    <col min="6" max="6" width="14.5" customWidth="1"/>
-    <col min="7" max="7" width="21.25" customWidth="1"/>
-    <col min="8" max="8" width="24.875" customWidth="1"/>
-    <col min="9" max="9" width="13.175" customWidth="1"/>
-    <col min="10" max="10" width="16.0083333333333" customWidth="1"/>
-    <col min="11" max="11" width="26.8416666666667" customWidth="1"/>
-    <col min="12" max="12" width="23.675" customWidth="1"/>
-    <col min="13" max="13" width="22.0083333333333" customWidth="1"/>
-    <col min="14" max="14" width="28.125" customWidth="1"/>
+    <col min="3" max="3" width="16.0083333333333" customWidth="1"/>
+    <col min="4" max="5" width="22.175" customWidth="1"/>
+    <col min="6" max="6" width="12.3416666666667" customWidth="1"/>
+    <col min="7" max="8" width="14.3416666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.0083333333333" customWidth="1"/>
+    <col min="10" max="10" width="23.675" customWidth="1"/>
+    <col min="11" max="13" width="12.3416666666667" customWidth="1"/>
+    <col min="14" max="14" width="10.5083333333333" customWidth="1"/>
+    <col min="15" max="15" width="16.0083333333333" customWidth="1"/>
+    <col min="16" max="16" width="26.8416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="22.5" customHeight="1" spans="1:16">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:16">
+      <c r="A2" s="4">
+        <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="5">
         <v>5</v>
       </c>
-      <c r="E2" s="2">
+      <c r="G2" s="6">
         <v>15000</v>
       </c>
-      <c r="F2" s="2">
+      <c r="H2" s="6">
         <v>25000</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="2">
+      <c r="L2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="5">
         <v>13800138000</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>22</v>
+      <c r="P2" s="5" t="s">
+        <v>25</v>
       </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:16">
+      <c r="A3" s="7"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:16">
+      <c r="A4" s="7"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:16">
+      <c r="A5" s="7"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:16">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:16">
+      <c r="A7" s="7"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:16">
+      <c r="A8" s="7"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:16">
+      <c r="A9" s="7"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:16">
+      <c r="A10" s="7"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:16">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:16">
+      <c r="A12" s="7"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:16">
+      <c r="A13" s="7"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:16">
+      <c r="A14" s="7"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:16">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:16">
+      <c r="A17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:16">
+      <c r="A18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:16">
+      <c r="A19" s="7"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:16">
+      <c r="A20" s="7"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:16">
+      <c r="A21" s="7"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:16">
+      <c r="A22" s="7"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:16">
+      <c r="A23" s="7"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:16">
+      <c r="A24" s="7"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:16">
+      <c r="A25" s="7"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:16">
+      <c r="A26" s="7"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:16">
+      <c r="A27" s="7"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:16">
+      <c r="A28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:16">
+      <c r="A29" s="7"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:16">
+      <c r="A30" s="7"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:16">
+      <c r="A31" s="7"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:16">
+      <c r="A32" s="7"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:16">
+      <c r="A33" s="7"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:16">
+      <c r="A34" s="7"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:16">
+      <c r="A35" s="7"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+    </row>
+    <row r="36" ht="16.5" spans="1:16">
+      <c r="A36" s="7"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:16">
+      <c r="A37" s="7"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:16">
+      <c r="A38" s="7"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:16">
+      <c r="A39" s="7"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" ht="16.5" spans="1:16">
+      <c r="A40" s="7"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+    </row>
+    <row r="41" ht="16.5" spans="1:16">
+      <c r="A41" s="7"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+    </row>
+    <row r="42" ht="16.5" spans="1:16">
+      <c r="A42" s="7"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+    </row>
+    <row r="43" ht="16.5" spans="1:16">
+      <c r="A43" s="7"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+    </row>
+    <row r="44" ht="16.5" spans="1:16">
+      <c r="A44" s="7"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+    </row>
+    <row r="45" ht="16.5" spans="1:16">
+      <c r="A45" s="7"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+    </row>
+    <row r="46" ht="16.5" spans="1:16">
+      <c r="A46" s="7"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" ht="16.5" spans="1:16">
+      <c r="A47" s="7"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+    </row>
+    <row r="48" ht="16.5" spans="1:16">
+      <c r="A48" s="7"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+    </row>
+    <row r="49" ht="16.5" spans="1:16">
+      <c r="A49" s="7"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+    </row>
+    <row r="50" ht="16.5" spans="1:16">
+      <c r="A50" s="7"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+    </row>
+    <row r="51" ht="16.5" spans="1:16">
+      <c r="A51" s="7"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+    </row>
+    <row r="52" ht="16.5" spans="1:16">
+      <c r="A52" s="7"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:16">
+      <c r="A53" s="7"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+    </row>
+    <row r="54" ht="16.5" spans="1:16">
+      <c r="A54" s="7"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+    </row>
+    <row r="55" ht="16.5" spans="1:16">
+      <c r="A55" s="7"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+    </row>
+    <row r="56" ht="16.5" spans="1:16">
+      <c r="A56" s="7"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+    </row>
+    <row r="57" ht="16.5" spans="1:16">
+      <c r="A57" s="7"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+    </row>
+    <row r="58" ht="16.5" spans="1:16">
+      <c r="A58" s="7"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:16">
+      <c r="A59" s="7"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:16">
+      <c r="A60" s="7"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:16">
+      <c r="A61" s="7"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:16">
+      <c r="A62" s="7"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+    </row>
+    <row r="63" ht="16.5" spans="1:16">
+      <c r="A63" s="7"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+    </row>
+    <row r="64" ht="16.5" spans="1:16">
+      <c r="A64" s="7"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+    </row>
+    <row r="65" ht="16.5" spans="1:16">
+      <c r="A65" s="7"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+    </row>
+    <row r="66" ht="16.5" spans="1:16">
+      <c r="A66" s="7"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+    </row>
+    <row r="67" ht="16.5" spans="1:16">
+      <c r="A67" s="7"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+    </row>
+    <row r="68" ht="16.5" spans="1:16">
+      <c r="A68" s="7"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+    </row>
+    <row r="69" ht="16.5" spans="1:16">
+      <c r="A69" s="7"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:16">
+      <c r="A70" s="7"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+    </row>
+    <row r="71" ht="16.5" spans="1:16">
+      <c r="A71" s="7"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:16">
+      <c r="A72" s="7"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:16">
+      <c r="A73" s="7"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+    </row>
+    <row r="74" ht="16.5" spans="1:16">
+      <c r="A74" s="7"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:16">
+      <c r="A75" s="7"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:16">
+      <c r="A76" s="7"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+    </row>
+    <row r="77" ht="16.5" spans="1:16">
+      <c r="A77" s="7"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+    </row>
+    <row r="78" ht="16.5" spans="1:16">
+      <c r="A78" s="7"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+    </row>
+    <row r="79" ht="16.5" spans="1:16">
+      <c r="A79" s="7"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+    </row>
+    <row r="80" ht="16.5" spans="1:16">
+      <c r="A80" s="7"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+    </row>
+    <row r="81" ht="16.5" spans="1:16">
+      <c r="A81" s="7"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+    </row>
+    <row r="82" ht="16.5" spans="1:16">
+      <c r="A82" s="7"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+    </row>
+    <row r="83" ht="16.5" spans="1:16">
+      <c r="A83" s="7"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+    </row>
+    <row r="84" ht="16.5" spans="1:16">
+      <c r="A84" s="7"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+    </row>
+    <row r="85" ht="16.5" spans="1:16">
+      <c r="A85" s="7"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+    </row>
+    <row r="86" ht="16.5" spans="1:16">
+      <c r="A86" s="7"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="5"/>
+    </row>
+    <row r="87" ht="16.5" spans="1:16">
+      <c r="A87" s="7"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5"/>
+    </row>
+    <row r="88" ht="16.5" spans="1:16">
+      <c r="A88" s="7"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5"/>
+    </row>
+    <row r="89" ht="16.5" spans="1:16">
+      <c r="A89" s="7"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+    </row>
+    <row r="90" ht="16.5" spans="1:16">
+      <c r="A90" s="7"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="5"/>
+    </row>
+    <row r="91" ht="16.5" spans="1:16">
+      <c r="A91" s="7"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+    </row>
+    <row r="92" ht="16.5" spans="1:16">
+      <c r="A92" s="7"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+    </row>
+    <row r="93" ht="16.5" spans="1:16">
+      <c r="A93" s="7"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5"/>
+    </row>
+    <row r="94" ht="16.5" spans="1:16">
+      <c r="A94" s="7"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="5"/>
+    </row>
+    <row r="95" ht="16.5" spans="1:16">
+      <c r="A95" s="7"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
+      <c r="P95" s="5"/>
+    </row>
+    <row r="96" ht="16.5" spans="1:16">
+      <c r="A96" s="7"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="5"/>
+    </row>
+    <row r="97" ht="16.5" spans="1:16">
+      <c r="A97" s="7"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="5"/>
+    </row>
+    <row r="98" ht="16.5" spans="1:16">
+      <c r="A98" s="7"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5"/>
+    </row>
+    <row r="99" ht="16.5" spans="1:16">
+      <c r="A99" s="7"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5"/>
+    </row>
+    <row r="100" ht="16.5" spans="1:16">
+      <c r="A100" s="7"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5"/>
+    </row>
+    <row r="101" ht="16.5" spans="1:16">
+      <c r="A101" s="7"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="5"/>
+    </row>
+    <row r="102" ht="16.5" spans="1:16">
+      <c r="A102" s="7"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5"/>
+      <c r="P102" s="5"/>
+    </row>
+    <row r="103" ht="16.5" spans="1:16">
+      <c r="A103" s="7"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="5"/>
+    </row>
+    <row r="104" ht="16.5" spans="1:16">
+      <c r="A104" s="7"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+    </row>
+    <row r="105" ht="16.5" spans="1:16">
+      <c r="A105" s="7"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5"/>
+    </row>
+    <row r="106" ht="16.5" spans="1:16">
+      <c r="A106" s="7"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+    </row>
+    <row r="107" ht="16.5" spans="1:16">
+      <c r="A107" s="7"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5"/>
+      <c r="P107" s="5"/>
+    </row>
+    <row r="108" ht="16.5" spans="1:16">
+      <c r="A108" s="7"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="5"/>
+    </row>
+    <row r="109" ht="16.5" spans="1:16">
+      <c r="A109" s="7"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
+    </row>
+    <row r="110" ht="16.5" spans="1:16">
+      <c r="A110" s="7"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+    </row>
+    <row r="111" ht="16.5" spans="1:16">
+      <c r="A111" s="7"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+    </row>
+    <row r="112" ht="16.5" spans="1:16">
+      <c r="A112" s="7"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5"/>
+      <c r="P112" s="5"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
